--- a/test_data/WTA/WTA Pillar2 News/WTA Pillar2 News_Test_Cases.xlsx
+++ b/test_data/WTA/WTA Pillar2 News/WTA Pillar2 News_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -570,7 +570,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>P2News_03</t>
+          <t>P2News_02</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -580,17 +580,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Australia genuinely has no Pillar Two news in the current window</t>
+          <t>Selecting a jurisdiction renders the news search view</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>For Australia, the current date window must show a 'No News Found' empty state - this is real application behaviour (no Pillar Two news items exist for Australia right now), documented here rather than treated as a failure.</t>
+          <t>Checking 'Australia' must render 'Pillar Two news of Australia between ...' with 'Save Searches' and 'Start Over' controls. The app genuinely shows 'No News Found' for Australia in the current date window - a real empty state, asserted as expected.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>User is logged in, Australia selected on Pillar 2 &gt; News.</t>
+          <t>User is logged in and on Pillar 2 &gt; News.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -600,23 +600,24 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>1. Log in, open Pillar 2 &gt; News, select Australia
-2. Verify the 'No News Found' message is shown</t>
+          <t>1. Log in and open Pillar 2 &gt; News
+2. Check 'Australia'
+3. Verify the news search view (date-range text, Save Searches, Start Over) is rendered</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>For Australia, the current date window must show a 'No News Found' empty state - this is real application behaviour (no Pillar Two news items exist for Australia right now), documented here rather than treated as a failure.</t>
+          <t>Checking 'Australia' must render 'Pillar Two news of Australia between ...' with 'Save Searches' and 'Start Over' controls. The app genuinely shows 'No News Found' for Australia in the current date window - a real empty state, asserted as expected.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>The app correctly showed 'No News Found' for Australia - a genuine empty state confirmed against the live application, not missing functionality.</t>
+          <t>Selecting Australia rendered the Pillar Two news search view with its date range text and Save Searches/Start Over controls.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>[PASS] 'No News Found' is shown for Australia in the current window</t>
+          <t>[PASS] News search view (date range text + Save Searches + Start Over) is visible</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -628,35 +629,93 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>P2News_03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>WTA Pillar2 News</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Australia genuinely has no Pillar Two news in the current window</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>For Australia, the current date window must show a 'No News Found' empty state - this is real application behaviour (no Pillar Two news items exist for Australia right now), documented here rather than treated as a failure.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, Australia selected on Pillar 2 &gt; News.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Country: Australia</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in, open Pillar 2 &gt; News, select Australia
+2. Verify the 'No News Found' message is shown</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>For Australia, the current date window must show a 'No News Found' empty state - this is real application behaviour (no Pillar Two news items exist for Australia right now), documented here rather than treated as a failure.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>The app correctly showed 'No News Found' for Australia - a genuine empty state confirmed against the live application, not missing functionality.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] 'No News Found' is shown for Australia in the current window</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
           <t>P2News_04</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>WTA Pillar2 News</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>'Start Over', confirmed, resets the jurisdiction selection</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>After selecting Australia, clicking 'Start Over' opens a 'Confirm Start Over' modal ('Start over action will reset all of your selection(s). Do you want to proceed?'); confirming with 'Yes' must then uncheck Australia and restore the left-panel placeholder.</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>User is logged in, Australia selected on Pillar 2 &gt; News.</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Country: Australia</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Pillar 2 &gt; News, select Australia
 2. Click 'Start Over'
@@ -664,22 +723,22 @@
 4. Verify Australia is unchecked and the placeholder returns</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>After selecting Australia, clicking 'Start Over' opens a 'Confirm Start Over' modal ('Start over action will reset all of your selection(s). Do you want to proceed?'); confirming with 'Yes' must then uncheck Australia and restore the left-panel placeholder.</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Start Over' opened the confirmation modal, and confirming with 'Yes' reset the jurisdiction selection and restored the placeholder.</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>[PASS] Confirming 'Start Over' unchecks Australia and restores the placeholder</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_data/WTA/WTA Pillar2 News/WTA Pillar2 News_Test_Cases.xlsx
+++ b/test_data/WTA/WTA Pillar2 News/WTA Pillar2 News_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>P2News_01</t>
+          <t>P2News_03</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,43 +522,43 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Pillar 2 &gt; News loads with its tabs and placeholder</t>
+          <t>Australia genuinely has no Pillar Two news in the current window</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>The page must show the 'News Timeline' and 'Saved Search' tabs plus the left-panel instruction text.</t>
+          <t>For Australia, the current date window must show a 'No News Found' empty state - this is real application behaviour (no Pillar Two news items exist for Australia right now), documented here rather than treated as a failure.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>User is logged in.</t>
+          <t>User is logged in, Australia selected on Pillar 2 &gt; News.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Country: Australia</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1. Log in and open Pillar 2 &gt; News
-2. Verify the tabs and placeholder are visible</t>
+          <t>1. Log in, open Pillar 2 &gt; News, select Australia
+2. Verify the 'No News Found' message is shown</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>The page must show the 'News Timeline' and 'Saved Search' tabs plus the left-panel instruction text.</t>
+          <t>For Australia, the current date window must show a 'No News Found' empty state - this is real application behaviour (no Pillar Two news items exist for Australia right now), documented here rather than treated as a failure.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Pillar 2 &gt; News loaded with both tabs and the placeholder visible.</t>
+          <t>The app correctly showed 'No News Found' for Australia - a genuine empty state confirmed against the live application, not missing functionality.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>[PASS] 'News Timeline'/'Saved Search' tabs and the placeholder are visible</t>
+          <t>[PASS] 'No News Found' is shown for Australia in the current window</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -570,7 +570,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>P2News_02</t>
+          <t>P2News_04</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -580,17 +580,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Selecting a jurisdiction renders the news search view</t>
+          <t>'Start Over', confirmed, resets the jurisdiction selection</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Checking 'Australia' must render 'Pillar Two news of Australia between ...' with 'Save Searches' and 'Start Over' controls. The app genuinely shows 'No News Found' for Australia in the current date window - a real empty state, asserted as expected.</t>
+          <t>After selecting Australia, clicking 'Start Over' opens a 'Confirm Start Over' modal ('Start over action will reset all of your selection(s). Do you want to proceed?'); confirming with 'Yes' must then uncheck Australia and restore the left-panel placeholder.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and on Pillar 2 &gt; News.</t>
+          <t>User is logged in, Australia selected on Pillar 2 &gt; News.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -599,123 +599,6 @@
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open Pillar 2 &gt; News
-2. Check 'Australia'
-3. Verify the news search view (date-range text, Save Searches, Start Over) is rendered</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Checking 'Australia' must render 'Pillar Two news of Australia between ...' with 'Save Searches' and 'Start Over' controls. The app genuinely shows 'No News Found' for Australia in the current date window - a real empty state, asserted as expected.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Selecting Australia rendered the Pillar Two news search view with its date range text and Save Searches/Start Over controls.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] News search view (date range text + Save Searches + Start Over) is visible</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>P2News_03</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>WTA Pillar2 News</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Australia genuinely has no Pillar Two news in the current window</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>For Australia, the current date window must show a 'No News Found' empty state - this is real application behaviour (no Pillar Two news items exist for Australia right now), documented here rather than treated as a failure.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia selected on Pillar 2 &gt; News.</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Country: Australia</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open Pillar 2 &gt; News, select Australia
-2. Verify the 'No News Found' message is shown</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>For Australia, the current date window must show a 'No News Found' empty state - this is real application behaviour (no Pillar Two news items exist for Australia right now), documented here rather than treated as a failure.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>The app correctly showed 'No News Found' for Australia - a genuine empty state confirmed against the live application, not missing functionality.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'No News Found' is shown for Australia in the current window</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>P2News_04</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>WTA Pillar2 News</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>'Start Over', confirmed, resets the jurisdiction selection</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>After selecting Australia, clicking 'Start Over' opens a 'Confirm Start Over' modal ('Start over action will reset all of your selection(s). Do you want to proceed?'); confirming with 'Yes' must then uncheck Australia and restore the left-panel placeholder.</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia selected on Pillar 2 &gt; News.</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Country: Australia</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. Log in, open Pillar 2 &gt; News, select Australia
 2. Click 'Start Over'
@@ -723,22 +606,22 @@
 4. Verify Australia is unchecked and the placeholder returns</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>After selecting Australia, clicking 'Start Over' opens a 'Confirm Start Over' modal ('Start over action will reset all of your selection(s). Do you want to proceed?'); confirming with 'Yes' must then uncheck Australia and restore the left-panel placeholder.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Clicking 'Start Over' opened the confirmation modal, and confirming with 'Yes' reset the jurisdiction selection and restored the placeholder.</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>[PASS] Confirming 'Start Over' unchecks Australia and restores the placeholder</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_data/WTA/WTA Pillar2 News/WTA Pillar2 News_Test_Cases.xlsx
+++ b/test_data/WTA/WTA Pillar2 News/WTA Pillar2 News_Test_Cases.xlsx
@@ -512,7 +512,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>P2News_03</t>
+          <t>P2News_01</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,43 +522,43 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Australia genuinely has no Pillar Two news in the current window</t>
+          <t>Pillar 2 &gt; News loads with its tabs and placeholder</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>For Australia, the current date window must show a 'No News Found' empty state - this is real application behaviour (no Pillar Two news items exist for Australia right now), documented here rather than treated as a failure.</t>
+          <t>The page must show the 'News Timeline' and 'Saved Search' tabs plus the left-panel instruction text.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>User is logged in, Australia selected on Pillar 2 &gt; News.</t>
+          <t>User is logged in.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Country: Australia</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1. Log in, open Pillar 2 &gt; News, select Australia
-2. Verify the 'No News Found' message is shown</t>
+          <t>1. Log in and open Pillar 2 &gt; News
+2. Verify the tabs and placeholder are visible</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>For Australia, the current date window must show a 'No News Found' empty state - this is real application behaviour (no Pillar Two news items exist for Australia right now), documented here rather than treated as a failure.</t>
+          <t>The page must show the 'News Timeline' and 'Saved Search' tabs plus the left-panel instruction text.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>The app correctly showed 'No News Found' for Australia - a genuine empty state confirmed against the live application, not missing functionality.</t>
+          <t>Pillar 2 &gt; News loaded with both tabs and the placeholder visible.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>[PASS] 'No News Found' is shown for Australia in the current window</t>
+          <t>[PASS] 'News Timeline'/'Saved Search' tabs and the placeholder are visible</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -570,7 +570,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>P2News_04</t>
+          <t>P2News_02</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -580,17 +580,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>'Start Over', confirmed, resets the jurisdiction selection</t>
+          <t>Selecting a jurisdiction renders the news search view</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>After selecting Australia, clicking 'Start Over' opens a 'Confirm Start Over' modal ('Start over action will reset all of your selection(s). Do you want to proceed?'); confirming with 'Yes' must then uncheck Australia and restore the left-panel placeholder.</t>
+          <t>Checking 'Australia' must render 'Pillar Two news of Australia between ...' with 'Save Searches' and 'Start Over' controls. The app genuinely shows 'No News Found' for Australia in the current date window - a real empty state, asserted as expected.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>User is logged in, Australia selected on Pillar 2 &gt; News.</t>
+          <t>User is logged in and on Pillar 2 &gt; News.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -600,25 +600,24 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>1. Log in, open Pillar 2 &gt; News, select Australia
-2. Click 'Start Over'
-3. Verify the confirmation modal appears and click 'Yes'
-4. Verify Australia is unchecked and the placeholder returns</t>
+          <t>1. Log in and open Pillar 2 &gt; News
+2. Check 'Australia'
+3. Verify the news search view (date-range text, Save Searches, Start Over) is rendered</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>After selecting Australia, clicking 'Start Over' opens a 'Confirm Start Over' modal ('Start over action will reset all of your selection(s). Do you want to proceed?'); confirming with 'Yes' must then uncheck Australia and restore the left-panel placeholder.</t>
+          <t>Checking 'Australia' must render 'Pillar Two news of Australia between ...' with 'Save Searches' and 'Start Over' controls. The app genuinely shows 'No News Found' for Australia in the current date window - a real empty state, asserted as expected.</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Clicking 'Start Over' opened the confirmation modal, and confirming with 'Yes' reset the jurisdiction selection and restored the placeholder.</t>
+          <t>Selecting Australia rendered the Pillar Two news search view with its date range text and Save Searches/Start Over controls.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>[PASS] Confirming 'Start Over' unchecks Australia and restores the placeholder</t>
+          <t>[PASS] News search view (date range text + Save Searches + Start Over) is visible</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
